--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D2">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="D3">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="G3">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="H3">
         <v>426</v>
